--- a/branches/fix/german-menu-and-footer/all-profiles.xlsx
+++ b/branches/fix/german-menu-and-footer/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T21:56:01+00:00</t>
+    <t>2026-07-25T21:59:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
